--- a/it_forms/009_dynamic_dropdown_test_form--it_forms.xlsx
+++ b/it_forms/009_dynamic_dropdown_test_form--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Select First</t>
+          <t>What is your favorite color?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Select Second</t>
+          <t>What is your favorite food?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Select Third</t>
+          <t>How many siblings do you have?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>select_first</t>
+          <t>select_fourth</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Select First</t>
+          <t>What is your favorite season?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>select_second</t>
+          <t>select_fifth</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Select Second</t>
+          <t>What is your favorite month?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>select_third</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Select Third</t>
+          <t>Text</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>select_third</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Select Third</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Text</t>
+          <t>Decimal</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,21 +745,44 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Select One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>select_two</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Select Two</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -776,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -826,121 +849,121 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_second_choices</t>
+          <t>select_first_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_second_choices</t>
+          <t>select_first_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_third_choices</t>
+          <t>select_second_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>pizza</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Pizza</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_third_choices</t>
+          <t>select_second_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>burger</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Burger</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_first_choices</t>
+          <t>select_second_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>sushi</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sushi</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_first_choices</t>
+          <t>select_second_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>salad</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Salad</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_second_choices</t>
+          <t>select_third_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -957,7 +980,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_second_choices</t>
+          <t>select_third_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -979,63 +1002,386 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_third_choices</t>
+          <t>select_fourth_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Spring</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_third_choices</t>
+          <t>select_fourth_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>summer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Summer</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_third_choices</t>
+          <t>select_fourth_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>autumn</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>Autumn</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>select_fourth_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>winter</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Winter</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>select_fifth_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>january</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>select_fifth_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>february</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>select_fifth_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>march</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>select_fifth_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>april</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>select_fifth_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>may</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>select_fifth_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>june</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>select_fifth_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>select_fifth_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>august</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>August</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>select_fifth_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>september</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>September</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>select_fifth_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>october</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>select_fifth_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>november</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>November</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>select_fifth_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>december</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>select_one_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>select_one_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>select_one_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>select_two_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>select_two_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>select_two_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
